--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="16">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.61</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="17">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="16">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="17">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>

--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="16">
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="17">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -698,7 +698,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>* Best Model: Complement NB: Achieved 95.0% accuracy and 94.2% F1 score with 95.2% cross-validation mean.</t>
+          <t>* Best Model: Complement NB: Achieved 95.0% accuracy and 94.2% F1 score with 89.3% cross-validation mean.</t>
         </is>
       </c>
     </row>
@@ -6549,31 +6549,33 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>N/A%</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>N/A%</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>N/A%</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>N/A%</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>90.1%</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>0.33</v>
+          <t>N/A%</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -6584,31 +6586,31 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -6639,11 +6641,11 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="17">
@@ -6654,31 +6656,31 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>

--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="16">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="17">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>

--- a/static/outputs/lumiq_report.xlsx
+++ b/static/outputs/lumiq_report.xlsx
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="16">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
